--- a/Result/profitability/1445.xlsx
+++ b/Result/profitability/1445.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.29875</v>
+        <v>-0.30625</v>
       </c>
       <c r="N2" t="n">
-        <v>5.134999999999999</v>
+        <v>4.381249999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.23</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.24625</v>
+        <v>-0.10875</v>
       </c>
       <c r="N3" t="n">
-        <v>5.667499999999999</v>
+        <v>10.84625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.07124999999999998</v>
+        <v>-0.125</v>
       </c>
       <c r="N4" t="n">
-        <v>11.73</v>
+        <v>9.51125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>-0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.105</v>
+        <v>-0.06374999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9.734999999999999</v>
+        <v>8.26375</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.02124999999999999</v>
+        <v>-0.03249999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>9.594999999999999</v>
+        <v>8.309999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01375000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="N7" t="n">
-        <v>10.06125</v>
+        <v>9.1775</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06125000000000001</v>
+        <v>0.02625</v>
       </c>
       <c r="N8" t="n">
-        <v>10.51125</v>
+        <v>7.365</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05750000000000001</v>
+        <v>0.0575</v>
       </c>
       <c r="N9" t="n">
-        <v>8.397499999999999</v>
+        <v>8.397500000000001</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
         <v>0.13125</v>
       </c>
       <c r="N12" t="n">
-        <v>7.74375</v>
+        <v>7.743749999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>136</v>
+      </c>
+      <c r="D75" t="n">
+        <v>137</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-18.69%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-34</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-33</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.3275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.059999999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-9.333333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-25.17</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-1.021095334685598</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5689655172413792</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-11.77</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.046222222222222</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
